--- a/reports/Debug-purgatory-20260111/For The Day (Prior Year)_Visits.xlsx
+++ b/reports/Debug-purgatory-20260111/For The Day (Prior Year)_Visits.xlsx
@@ -34,10 +34,10 @@
     <t>Purgatory Passes</t>
   </si>
   <si>
+    <t>Purgatory Comp Tickets</t>
+  </si>
+  <si>
     <t>Purgatory Coaster</t>
-  </si>
-  <si>
-    <t>Purgatory Comp Tickets</t>
   </si>
   <si>
     <t>Purgatory Tickets</t>
@@ -434,7 +434,7 @@
         <v>45669</v>
       </c>
       <c r="C2" s="2">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,7 +448,7 @@
         <v>45669</v>
       </c>
       <c r="C3" s="2">
-        <v>126</v>
+        <v>26</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -462,7 +462,7 @@
         <v>45669</v>
       </c>
       <c r="C4" s="2">
-        <v>28</v>
+        <v>173</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>6</v>
@@ -476,7 +476,7 @@
         <v>45669</v>
       </c>
       <c r="C5" s="2">
-        <v>26</v>
+        <v>1847</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>5</v>
@@ -490,7 +490,7 @@
         <v>45669</v>
       </c>
       <c r="C6" s="2">
-        <v>173</v>
+        <v>28</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>7</v>
@@ -518,7 +518,7 @@
         <v>45669</v>
       </c>
       <c r="C8" s="2">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>5</v>
@@ -532,7 +532,7 @@
         <v>45669</v>
       </c>
       <c r="C9" s="2">
-        <v>1847</v>
+        <v>126</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>5</v>
